--- a/tags.xlsx
+++ b/tags.xlsx
@@ -5,15 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EntraId\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EntraId\EntraID\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A92B906-7A5F-41A4-BAC0-A1EB5884176D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{688C6BCC-4DAE-44F3-A148-E81BDF31B543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="521" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="option1" sheetId="1" r:id="rId1"/>
+    <sheet name="option2" sheetId="2" r:id="rId2"/>
+    <sheet name="option3" sheetId="3" r:id="rId3"/>
+    <sheet name="inlinepolicy" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="53">
   <si>
     <t>customerservice</t>
   </si>
@@ -69,9 +72,6 @@
     <t>Developer</t>
   </si>
   <si>
-    <t>aws-grp-customerservice-developer-dev-nonprod</t>
-  </si>
-  <si>
     <t xml:space="preserve">dev </t>
   </si>
   <si>
@@ -81,9 +81,6 @@
     <t>test</t>
   </si>
   <si>
-    <t>aws-grp-customerservice-developer-Staging-nonprod</t>
-  </si>
-  <si>
     <t>stage</t>
   </si>
   <si>
@@ -93,10 +90,6 @@
     <t>CustomerService</t>
   </si>
   <si>
-    <t>project=Loans,
-Environment=Dev</t>
-  </si>
-  <si>
     <t>AWS-Developer-CS-Dev</t>
   </si>
   <si>
@@ -122,16 +115,299 @@
   </si>
   <si>
     <t>Environment</t>
+  </si>
+  <si>
+    <t>Developer-Dev</t>
+  </si>
+  <si>
+    <t>Developer-Test</t>
+  </si>
+  <si>
+    <t>Developer-Stage</t>
+  </si>
+  <si>
+    <t>AWS-Developer-CS-Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policy Condition  </t>
+  </si>
+  <si>
+    <t>Condition include for loans</t>
+  </si>
+  <si>
+    <t>Condition include for payments</t>
+  </si>
+  <si>
+    <t>aws-grp-customerservice-dev-nonprod</t>
+  </si>
+  <si>
+    <t>aws-grp-customerservice-Test-nonprod</t>
+  </si>
+  <si>
+    <t>aws-grp-customerservice-Staging-nonprod</t>
+  </si>
+  <si>
+    <t>Account</t>
+  </si>
+  <si>
+    <t>AWS-Developer-Dev</t>
+  </si>
+  <si>
+    <t>AWS-Developer-Test</t>
+  </si>
+  <si>
+    <t>AWS-Developer-stage</t>
+  </si>
+  <si>
+    <t>aws-grp-customerservice-developer-Dev-nonprod</t>
+  </si>
+  <si>
+    <t>aws-grp-customerservice-developer-Stage-nonprod</t>
+  </si>
+  <si>
+    <t>account name</t>
+  </si>
+  <si>
+    <t>projectname=blue</t>
+  </si>
+  <si>
+    <t>N1-dev</t>
+  </si>
+  <si>
+    <t>projectname=red</t>
+  </si>
+  <si>
+    <t>N2-dev</t>
+  </si>
+  <si>
+    <t>{
+  "Version": "2012-10-17",
+  "Statement": [
+    {
+      "Sid": "ReadOnlyDiscovery",
+      "Effect": "Allow",
+      "Action": [
+        "ec2:DescribeInstances",
+        "ec2:DescribeVolumes",
+        "ec2:DescribeTags",
+        "ec2:DescribeImages",
+        "ec2:DescribeSubnets",
+        "ec2:DescribeSecurityGroups",
+        "ec2:DescribeVpcs",
+        "lambda:GetFunction",
+        "lambda:GetFunctionConfiguration",
+        "lambda:ListFunctions",
+        "lambda:ListTags",
+        "s3:ListAllMyBuckets",
+        "s3:GetBucketLocation",
+        "s3:GetBucketTagging"
+      ],
+      "Resource": "*"
+    },
+    {
+      "Sid": "AllowRunInstancesOnlyWithMatchingProjectTag",
+      "Effect": "Allow",
+      "Action": [
+        "ec2:RunInstances"
+      ],
+      "Resource": "*",
+      "Condition": {
+        "StringEquals": {
+          "aws:RequestTag/projectname": "${aws:PrincipalTag/projectname}"
+        },
+        "ForAllValues:StringEquals": {
+          "aws:TagKeys": [
+            "projectname"
+          ]
+        }
+      }
+    },
+    {
+      "Sid": "AllowCreateTagsOnlyDuringEC2Create",
+      "Effect": "Allow",
+      "Action": [
+        "ec2:CreateTags"
+      ],
+      "Resource": "*",
+      "Condition": {
+        "StringEquals": {
+          "ec2:CreateAction": "RunInstances",
+          "aws:RequestTag/projectname": "${aws:PrincipalTag/projectname}"
+        },
+        "ForAllValues:StringEquals": {
+          "aws:TagKeys": [
+            "projectname"
+          ]
+        }
+      }
+    },
+    {
+      "Sid": "AllowOperateOnlyOnMatchingEC2Resources",
+      "Effect": "Allow",
+      "Action": [
+        "ec2:StartInstances",
+        "ec2:StopInstances",
+        "ec2:RebootInstances",
+        "ec2:TerminateInstances"
+      ],
+      "Resource": "arn:aws:ec2:*:*:instance/*",
+      "Condition": {
+        "StringEquals": {
+          "ec2:ResourceTag/projectname": "${aws:PrincipalTag/projectname}"
+        }
+      }
+    },
+    {
+      "Sid": "AllowCreateLambdaOnlyWithMatchingProjectTag",
+      "Effect": "Allow",
+      "Action": [
+        "lambda:CreateFunction"
+      ],
+      "Resource": "arn:aws:lambda:*:*:function:*",
+      "Condition": {
+        "StringEquals": {
+          "aws:RequestTag/projectname": "${aws:PrincipalTag/projectname}"
+        },
+        "ForAllValues:StringEquals": {
+          "aws:TagKeys": [
+            "projectname"
+          ]
+        }
+      }
+    },
+    {
+      "Sid": "AllowTagLambdaOnlyWithMatchingProjectTag",
+      "Effect": "Allow",
+      "Action": [
+        "lambda:TagResource"
+      ],
+      "Resource": "arn:aws:lambda:*:*:function:*",
+      "Condition": {
+        "StringEquals": {
+          "aws:RequestTag/projectname": "${aws:PrincipalTag/projectname}"
+        },
+        "ForAllValues:StringEquals": {
+          "aws:TagKeys": [
+            "projectname"
+          ]
+        }
+      }
+    },
+    {
+      "Sid": "AllowOperateOnlyOnMatchingLambdaFunctions",
+      "Effect": "Allow",
+      "Action": [
+        "lambda:InvokeFunction",
+        "lambda:UpdateFunctionCode",
+        "lambda:UpdateFunctionConfiguration",
+        "lambda:DeleteFunction"
+      ],
+      "Resource": "arn:aws:lambda:*:*:function:*",
+      "Condition": {
+        "StringEquals": {
+          "aws:ResourceTag/projectname": "${aws:PrincipalTag/projectname}"
+        }
+      }
+    },
+    {
+      "Sid": "AllowCreateBucketOnlyWithMatchingProjectTag",
+      "Effect": "Allow",
+      "Action": [
+        "s3:CreateBucket",
+        "s3:PutBucketTagging"
+      ],
+      "Resource": "arn:aws:s3:::*",
+      "Condition": {
+        "StringEquals": {
+          "aws:RequestTag/projectname": "${aws:PrincipalTag/projectname}"
+        },
+        "ForAllValues:StringEquals": {
+          "aws:TagKeys": [
+            "projectname"
+          ]
+        }
+      }
+    },
+    {
+      "Sid": "AllowBucketAdminOnlyOnMatchingBuckets",
+      "Effect": "Allow",
+      "Action": [
+        "s3:GetBucketTagging",
+        "s3:PutBucketTagging",
+        "s3:DeleteBucket"
+      ],
+      "Resource": "arn:aws:s3:::*",
+      "Condition": {
+        "StringEquals": {
+          "aws:ResourceTag/projectname": "${aws:PrincipalTag/projectname}"
+        }
+      }
+    },
+    {
+      "Sid": "DenyChangingProjectTagAfterCreate",
+      "Effect": "Deny",
+      "Action": [
+        "ec2:CreateTags",
+        "ec2:DeleteTags",
+        "lambda:TagResource",
+        "lambda:UntagResource",
+        "s3:PutBucketTagging",
+        "s3:DeleteBucketTagging"
+      ],
+      "Resource": "*",
+      "Condition": {
+        "ForAnyValue:StringEquals": {
+          "aws:TagKeys": [
+            "projectname"
+          ]
+        }
+      }
+    },
+    {
+      "Sid": "DenyPrivilegeEscalation",
+      "Effect": "Deny",
+      "Action": [
+        "iam:*",
+        "organizations:*",
+        "account:*",
+        "sso:*",
+        "identitystore:*"
+      ],
+      "Resource": "*"
+    }
+  ]
+}</t>
+  </si>
+  <si>
+    <t>It allows read-only discovery, lets the user create EC2 instances, Lambda functions, and S3 buckets only when the request carries projectname equal to the user’s principal tag, and lets them operate only on already-tagged EC2 instances, Lambda functions, and S3 buckets whose projectname matches the same value. For EC2 tag-on-create, AWS requires both the create action and ec2:CreateTags, and supports constraining tagging with ec2:CreateAction, aws:RequestTag, and aws:TagKeys. Lambda supports ABAC with request and resource tags as well.</t>
+  </si>
+  <si>
+    <t>Important S3 caveat
+This policy is production-grade for S3 bucket administration, but not for object-level ABAC in a general-purpose bucket using plain bucket ARNs. AWS notes that aws:ResourceTag for S3 data access has important limitations, and for general-purpose buckets tag-based object access is typically done with S3 Access Points, object-tag conditions such as s3:ExistingObjectTag/..., or a design based on separate buckets/prefixes per project. So this policy safely covers bucket creation and bucket-level admin, but I would not claim it fully solves object-level least privilege unless you choose one of those S3 patterns.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -221,29 +497,49 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -526,12 +822,275 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:K13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" customWidth="1"/>
+    <col min="4" max="4" width="9.5546875" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="45.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="F2" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="F3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="F4" s="1"/>
+      <c r="G4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B8" s="14"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B9" s="14"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B10" s="14"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="11"/>
+    </row>
+    <row r="11" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B11" s="14"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B12" s="14"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B13" s="15"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K13" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B7:B13"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FD0F44C-3918-4E3C-8992-AA8E7EC833EC}">
   <dimension ref="B2:J13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5546875" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" customWidth="1"/>
     <col min="6" max="6" width="45.109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.77734375" bestFit="1" customWidth="1"/>
@@ -540,13 +1099,13 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
       <c r="F2" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
@@ -570,189 +1129,630 @@
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="B6" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H6" s="5" t="s">
+      <c r="G6" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>29</v>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>14</v>
+      <c r="F7" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="H7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B8" s="8"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B8" s="7"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="6" t="s">
-        <v>16</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>28</v>
+        <v>16</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B9" s="7"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="6" t="s">
-        <v>18</v>
+      <c r="B9" s="8"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>1</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B10" s="8"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B11" s="8"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="1" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-    </row>
-    <row r="11" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B11" s="7"/>
-      <c r="C11" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>29</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="6" t="s">
-        <v>14</v>
+      <c r="F11" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B12" s="8"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B12" s="7"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="6" t="s">
-        <v>16</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>28</v>
+        <v>16</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B13" s="4"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="6" t="s">
-        <v>18</v>
+      <c r="B13" s="9"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>26</v>
+        <v>17</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B7:B13"/>
   </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C35B061-6A0C-44BB-80AD-30B2053AAAD7}">
+  <dimension ref="B2:I21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5546875" customWidth="1"/>
+    <col min="5" max="5" width="45.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E2" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="E3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="E4" s="1"/>
+      <c r="F4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="16"/>
+      <c r="C8" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="16"/>
+      <c r="C9" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B10" s="16"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+    </row>
+    <row r="11" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="16"/>
+      <c r="C11" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="16"/>
+      <c r="C12" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="16"/>
+      <c r="C13" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B14" s="16"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B15" s="16"/>
+      <c r="C15" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B16" s="16"/>
+      <c r="C16" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B17" s="16"/>
+      <c r="C17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B18" s="16"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B19" s="16"/>
+      <c r="C19" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B20" s="16"/>
+      <c r="C20" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B21" s="16"/>
+      <c r="C21" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B7:B21"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F15CDB3A-40AD-4D0A-90E9-B25415864960}">
+  <dimension ref="D5:D9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="89" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="4:4" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="D5" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="4:4" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="D9" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>